--- a/artfynd/A 15197-2024 artfynd.xlsx
+++ b/artfynd/A 15197-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1331,6 +1331,113 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118066337</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94133</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hultabygget, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>390622</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6263194</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ränneslöv</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sanna Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sanna Persson, Mattias Lindström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15197-2024 artfynd.xlsx
+++ b/artfynd/A 15197-2024 artfynd.xlsx
@@ -1336,7 +1336,7 @@
         <v>118066337</v>
       </c>
       <c r="B7" t="n">
-        <v>94133</v>
+        <v>94135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 15197-2024 artfynd.xlsx
+++ b/artfynd/A 15197-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69225447</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91690598</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/320549</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56480945</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62069107</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118066337</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64376227</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118066361</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1714,6 +1759,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91691558</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1821,6 +1871,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107295470</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1923,8 +1978,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118066355</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>